--- a/leads_ALL.xlsx
+++ b/leads_ALL.xlsx
@@ -413,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -431,16 +431,19 @@
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
     <col width="17" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,6 +570,21 @@
       <c r="Y1" t="inlineStr">
         <is>
           <t>session</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>size_estimate</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>has_blog</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>has_english</t>
         </is>
       </c>
     </row>
@@ -654,6 +672,9 @@
           <t>20260515_143249</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -667,27 +688,27 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://vietnix.vn/agency-la-gi/</t>
+          <t>https://agencyvn.com/agency-la-gi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sales@vietnix.com.vn</t>
+          <t>trangnguyenthithuy@admicro.vn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>✅ Sales/HR</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>sales@vietnix.com.vn, support@vietnix.com.vn</t>
+          <t>trangnguyenthithuy@admicro.vn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0749259041, 0909686810, 0311850627</t>
+          <t>0981229151</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -702,25 +723,21 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/vietnix-hosting</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Agency tiếng việt là các công ty dịch vụ truyền thông quảng cáo cung cấp dịch vụ Marketing. Nhờ sự bùng nổ của Internet và công nghệ 4.0…</t>
+          <t>Agency là các công ty dịch vụ truyền thông quảng cáo cung cấp dịch vụ tiếp thị quảng cáo cho các công ty khác. Còn bạn Agency là gì ...</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -730,7 +747,7 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Sales/HR Email, Has Phone, VN Domain, IT Software, Multi-Email, LinkedIn</t>
+          <t>Has Phone, IT Software, Contact Page ✓, Services Page ✓, About Page ✓, Hiring</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -739,6 +756,9 @@
           <t>20260515_143249</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -747,32 +767,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://agencyvn.com/agency-la-gi</t>
+          <t>https://bachlongmobile.com/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trangnguyenthithuy@admicro.vn</t>
+          <t>director@bachlongmobile.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>🔥 Decision Maker</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>trangnguyenthithuy@admicro.vn</t>
+          <t>director@bachlongmobile.com, marketing@bachlongmobile.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0981229151</t>
+          <t>0931773036, 0913054934, 0908038038</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -786,22 +806,16 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Agency là các công ty dịch vụ truyền thông quảng cáo cung cấp dịch vụ tiếp thị quảng cáo cho các công ty khác. Còn bạn Agency là gì ...</t>
+          <t>Mua iPhone, iPad, MacBook, Apple Watch chính hãng VN/A tại Bachlongmobile.com - Đại lý ủy quyền Apple. Hỗ trợ thu cũ đổi mới, trả góp 0%, cùng khuyến mãi ngập tràn. Đặt hàng ngay để nhận ưu đãi HOT!</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -811,14 +825,25 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Contact Page ✓, Services Page ✓, About Page ✓, Hiring</t>
+          <t>Decision Maker Email, Has Phone, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -828,32 +853,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://agencyvn.com/agency-la-gi</t>
+          <t>https://saigontechnology.com/services/mobile-app-development/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trangnguyenthithuy@admicro.vn</t>
+          <t>sales@saigontechnology.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>✅ Sales/HR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>trangnguyenthithuy@admicro.vn</t>
+          <t>sales@saigontechnology.com, australia@saigontechnology.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0981229151</t>
+          <t>0313534747, 0767496612, 0545279210</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -867,22 +892,20 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/saigon-technology</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Agency là các công ty dịch vụ truyền thông quảng cáo cung cấp dịch vụ tiếp thị quảng cáo cho các công ty khác. Còn bạn Agency là gì ...</t>
+          <t>Mobile app development services for iOS, Android &amp; cross-platform apps. Trusted mobile app development company delivering scalable solutions.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -892,49 +915,60 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Contact Page ✓, Services Page ✓, About Page ✓, Hiring</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://remotepeople.com/glossary/outsourcing/</t>
+          <t>https://saigontechnology.com/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>info@remotepeople.com</t>
+          <t>sales@saigontechnology.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>✅ Sales/HR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>info@remotepeople.com</t>
+          <t>sales@saigontechnology.com, australia@saigontechnology.com, thanh.pham@saigontechnology.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0842767846</t>
+          <t>0313534747, 0767496612, 0383437732</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -948,26 +982,20 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/remotepeoplecom</t>
+          <t>https://linkedin.com/company/saigon-technology</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
+          <t>Saigon Technology is an ISO-certified Agile software development company in Vietnam, with headquarters in Ho Chi Minh City, three development centers, and over 400 engineers.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -977,49 +1005,60 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://remotepeople.com/glossary/outsourcing/</t>
+          <t>https://www.orientsoftware.com/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>info@remotepeople.com</t>
+          <t>sales@orientsoftware.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>✅ Sales/HR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>info@remotepeople.com</t>
+          <t>sales@orientsoftware.com, career@orientsoftware.com, contact@orientsoftware.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0842767846</t>
+          <t>0963736699, 0938390299</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1033,26 +1072,16 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/remotepeoplecom</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
+          <t>Trusted by 200+ global clients, Orient Software Development Corporation is a leading software development company in Vietnam delivering innovative solutions through flexible outsourcing service models.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1062,42 +1091,65 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>https://reliasoftware.com/industries/ecommerce-app-development</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sales@reliasoftware.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>✅ Sales/HR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>sales@reliasoftware.com</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0760182730, 0554503546, 0392421401</t>
+          <t>0972016100</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mobile Dev</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1106,22 +1158,20 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/relia-software</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Từ điển Hán Nôm - Tra từ: công</t>
+          <t>Looking for an E-commerce Mobile App Development Company? We Provide the best E-commerce mobile app development services for your business. Talk to us now!</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1131,42 +1181,65 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Has Phone, Mobile Dev</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>https://www.talentnetgroup.com/locations/ho-chi-minh-office</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>talentnet.cambodia@talentnetgroup.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>talentnet.cambodia@talentnetgroup.com, contact-hcm@talentnetgroup.com, mike.hebert@talentnetgroup.com</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0760182730, 0554503546, 0392421401</t>
+          <t>0949105144, 0854126856, 0305202145</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mobile Dev</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1175,22 +1248,20 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/talentnet-corporation</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Từ điển Hán Nôm - Tra từ: công</t>
+          <t>6th Floor, Star Building, 33 Mac Dinh Chi, District 1, Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1200,14 +1271,2981 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Has Phone, Mobile Dev</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://softvn.vn/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>email@domain.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>email@domain.com</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0868128213, 0868218213, 0578492573</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Mua, bán phần mềm bản quyền, software bản quyền chính hãng giá rẻ, giao hàng toàn quốc, dịch vụ triển khai chuyên nghiệp và nhanh chóng tại SOFTVN.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, IT Software, Hiring</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://tuyensinh.uel.edu.vn/nganh-cong-nghe-tai-chinh-la-gi/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>phonghanhchinh@uel.edu.vn</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>phonghanhchinh@uel.edu.vn, cntt@uel.edu.vn, tuvantuyensinh@uel.edu.vn</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0888247669, 0708247669</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Được xem là một làn sóng mới ưu việt, công nghệ tài chính Fintech đã làm thay đổi toàn bộ cách thức cung ứng, vận hành các dịch vụ tài chính. Cũng như mô hình tổ chức đã có từ trước đến nay. Vậy ngành công nghệ tài chính sẽ học những gì? Ở đâu đào tạo đảm bảo chất lượng và uy tín? Triển vọng nghề ng</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://genk.vn/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>giaitrixahoi@admicro.vn</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>giaitrixahoi@admicro.vn, info@genk.vn</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0965671778, 0522434621, 0596751139</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GenK là Website uy tín số 1 Việt Nam cung cấp cho bạn những thông tin mới nhất về công nghệ và thế giới Internet,tin tức sản phẩm cong nghe mới.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://hblabgroup.com/ai-outsourcing-company-in-vietnam/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>contact@hblab.vn</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>contact@hblab.vn, cs_gl@hblab.vn</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0983098304, 0362819068</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/hblab</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Choosing the right AI outsourcing company in Vietnam is a strategic decision shaped by talent depth, regulatory maturity, and the speed at which a partner can</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://civiloutsourcing.com/outsourcing-in-vietnam/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>contact@civiloutsourcing.com</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>contact@civiloutsourcing.com, aiden@civiloutsourcing.com</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0935012378, 0906013469</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/civil-engineering-outsourcing-services</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>As civil engineering and land survey firms face tighter deadlines, rising costs, and growing client demands, many are turning to global support to stay competitive. Among all outsourcing destinations, Vietnam outsourcing stands out as a strategic choice—especially for companies in the United States,</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://mobileworld.com.vn/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>support@mobileworld.com.vn</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>support@mobileworld.com.vn</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0965287989, 0961273979</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Hệ thống bán lẻ điện thoại, máy tính bảng, Smart watch tại Tp.HCM ✓Uy tín ✓Giá rẻ nhất ✓Trả góp 0% ✓Chính hãng ✓Giao toàn quốc. 0965 28 79 89</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, Mobile Dev, Hiring</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.jobthai.com/en/company/267137</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sale@jobthai.com</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>sale@jobthai.com, support@jobthai.com</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0929138383</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/jobthai</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Jobs at QAi Consulting and Services QAi Consulting, we are business partnership to providing consultancy services in many areas to help your business moving faster with high quality services deliver to customers and help transforming your business to digitalize organization.
+Today technology disr</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="AA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://digital-launch.com/web-development-outsourcing-vietnam/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>hello@digital-launch.com</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>hello@digital-launch.com</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0992229024, 0529488778, 0529565027</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/digital-launch.com</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Web development outsourcing Vietnam | Outsource your WordPress, Magento or custom web development to our skilled team in Ho Chi Minh City (Saigon)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://digital-launch.com/digital-agency-saigon/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>hello@digital-launch.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>hello@digital-launch.com</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0992229024, 0529488778, 0529565027</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/digital-launch.com</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Digital Agency in Saigon or Ho Chi Minh City that builds unique websites, does social media marketing and search engine optimization. Get ready to launch!</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://vietanlaw.com/utility-services-in-business-establishment-procedures-in-hanoi/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>info@vietanlaw.com</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>info@vietanlaw.com, info@vietanlaw.vn</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0984291372, 0577055285, 0805188828</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/viet-an-law</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Towards e-government suitable for the 4.0 technology era, the business registration procedure in Hanoi is considered a pioneering breakthrough in the</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://vietanlaw.com/fintech-company-establishment-in-vietnam-under-sandbox-regulatory/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>info@vietanlaw.com</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>info@vietanlaw.com, info@vietanlaw.vn</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0984291372, 0577055285, 0805188828</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/viet-an-law</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>The rapid rise of financial technology (Fintech) has brought profound changes to the financial and banking services sector, with the emergence of various</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.wdsaigon.com/e-commerce-website-development-vietnam/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>contact@wdsaigon.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>contact@wdsaigon.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0316755511, 0977163421</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/web-design-saigon</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Our e-commerce website development in Vietnam is designed to convert visitors to customers at your online store! Get a new Store Website Design.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://savvycomsoftware.com/services/it-outsourcing-services/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>contact@savvycomsoftware.com</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>contact@savvycomsoftware.com</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0352287866, 0703611494, 0903552656</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/765474</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Outsourcing Software Vietnam services will allow businesses to access expertise, improve core functions, benefit from scalability and security.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://dugarco.com/en/vietnam-clothing-manufacturers/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>dugarco@mayducgiang.com.vn</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>dugarco@mayducgiang.com.vn, info@dugarco.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0902156565</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Explore how to find Vietnam clothing manufacturers and the top 15 Vietnam Clothing Manufacturers 2026 such as Dugarco, Thygesen Textile,...</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://congcaphe.com/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>cmo@congcaphe.com</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>cmo@congcaphe.com, fr.intl@congcaphe.com, fr@congcaphe.com</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0911811123</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Mùa hè này, Cộng có mãng cầu.
+Còn bạn, chọn phiên bản “Ngầu” nào cho mình?</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://dagiac.com/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>dklong@dagiac.com</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>dklong@dagiac.com</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0949998844, 0570189432</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/dagiac</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>We are Full Service Digital Agency based in Ho Chi Minh helping foreign invested companies in Vietnam succeed with their Digital Marketing.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0312111054, 0971381476, 0525939362</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/iscale-solutions</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Outsource to Vietnam for high-quality, cost-efficient business services. Tap into skilled expertise and innovative solutions to boost your success. Book today!</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/ai-machine-learning-specialists/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0745102627, 0971381476, 0745101799</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/iscale-solutions</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Outsource AI &amp; machine learning, algorithms with a top company in Vietnam. Expert in artificial intelligence and software outsourcing solutions.</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.xtmobile.vn/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tinhlexuan@gmail.com</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>❌ Bad</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tinhlexuan@gmail.com, xtmobile.sg@gmail.com, xtmobile_sg@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0754716982, 0515113368, 0909410102</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Hệ thống bán lẻ điện thoại Samsung, iPhone mới - cũ, iPad, MacBook, phụ kiện chính hãng, thu cũ đổi mới. XTmobile có 7 cửa hàng tại TPHCM.</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email, Hiring</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>15</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://wearefram.com/services/mobile-app-development/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0821393511</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/fram</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Custom mobile app development services company in Vietnam. fram^ has dedicated teams with the best developers to build you custom solutions.</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>15</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nimblehq.co/locations/ho-chi-minh/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0948190247, 0347230347, 0887549738</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/nimblehq</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Nimble is a web software &amp; mobile application development company in Ho Chi Minh City, Vietnam. We build innovative &amp; top notch digital solutions.</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://wearefram.com/services/saas-development/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0821393511</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/fram</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Through an integrated and process-driven approach, fram^ offers SaaS development services needed for your product from start to finish.</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://innotech-vn.com/hire-mobile-app-developers-ios-android-in-vietnam/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0907896363</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/30204055</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Innotech Vietnam is reliable to hire mobile app developers (iOS/ Android) in Vietnam with the technically competent and creative bunch, attractive cost.</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.aegona.com/our-services/software-maintenance</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0704550073, 0914518869</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/aegona</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ensure the smooth operation of your software with expert software maintenance services and keep your software up-to-date, secure, and optimized for peak performance.</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://ondigitals.com/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>contact@ondigitals.com</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>contact@ondigitals.com</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0923150767, 0906648177, 0500363154</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/on-digitals</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Digital marketing services in HCMC, Vietnam from the top outsource marketing agency company, provide professional digital marketing solutions.</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://innotech-vn.com/top-ai-software-outsourcing-company-in-vietnam/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0907896363</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/30204055</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Building an internal AI engineering team is not only expensive but also time-consuming. This is why AI software outsourcing is becoming an increasingly...</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.startus-insights.com/innovators-guide/global-startup-ecosystem/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0588235294</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/startus</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Explore the 2026 startup ecosystem with insights on global rankings, capital flows, AI investments, and policies shaping innovation hubs worldwide.</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://remotepeople.com/glossary/outsourcing/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>info@remotepeople.com</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>info@remotepeople.com</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0842767846</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/remotepeoplecom</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>20260515_143249</t>
         </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://horusent.com/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0720231536, 0862595405, 0720232048</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>We are a mobile game company in Vietnam with more than 7 years of experience working in the international gaming industry.</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://crosstechcom.com/vietnam-web-development-company-revolutionizing-online-presence/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0741024107</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Learn how Vietnam's web development companies are revolutionizing online presence with quality, excellence, and cost-effective solutions. Look into offerings like digital marketing, mobile app development, e-commerce, and web design. Find the best web development company in Vietnam for your project</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>13</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.icloud.com/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0505161291</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Log in to iCloud to access your photos, mail, notes, documents and more. Sign in with your AppleÂ Account or create a new account to start using Apple services.</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev, Hiring</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.viivue.com/project-type/web-development/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0909690517</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/viivue-web-design-company</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Our process and thirst for knowledge enable us to design, redesign and build websites for clients across a wide range of industries — from education, hospitality, and healthcare to B2B services, manufacturing, and emerging technologies. We take time to understand each client’s business model, user n</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>11</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://phuoc-associates.com/practice/investment-in-viet-nam/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>info@phuoc-partner.com</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>info@phuoc-partner.com</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0822252301</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Web Design</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/phuoc-associates-law-firm</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Phuoc &amp; Associates one of the largest law firms in Vietnam, is a veteran specialist in providing legal services to foreign investors entering the Vietnamese market</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Has Phone, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0760182730, 0554503546, 0392421401</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Từ điển Hán Nôm - Tra từ: công</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>20260515_143249</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://msmobile.vn/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>msmobilevncom@gmail.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>❌ Bad</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>msmobilevncom@gmail.com, vandieutot@gmail.com</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0906655655, 0965112345, 0913087295</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Web Design</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>MSmobile chuyên bán điện thoại xách tay chính hãng, điện thoại cũ 99% giá rẻ, Máy tính bảng, Tablet, Phụ kiện chính hãng uy tín hàng đầu Việt Nam,msmobile.vn</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, Multi-Email</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/leads_ALL.xlsx
+++ b/leads_ALL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="b">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="b">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" t="b">
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="b">
@@ -839,10 +839,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="b">
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -929,10 +929,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="b">
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1019,10 +1019,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="b">
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1105,10 +1105,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="b">
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1195,10 +1195,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="b">
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1285,10 +1285,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="b">
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="b">
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1457,10 +1457,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="b">
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1543,10 +1543,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="b">
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1633,10 +1633,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="b">
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1723,10 +1723,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="b">
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1809,10 +1809,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="b">
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1900,10 +1900,10 @@
           <t>micro</t>
         </is>
       </c>
-      <c r="AA16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="b">
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1990,10 +1990,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="b">
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2080,10 +2080,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="b">
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2170,10 +2170,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="b">
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2260,10 +2260,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="b">
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2350,10 +2350,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB21" t="b">
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2440,10 +2440,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB22" t="b">
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2454,32 +2454,32 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://dugarco.com/en/vietnam-clothing-manufacturers/</t>
+          <t>https://digital-launch.com/digital-marketing-agency-in-vietnam/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>dugarco@mayducgiang.com.vn</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>dugarco@mayducgiang.com.vn, info@dugarco.com</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0902156565</t>
+          <t>0992229024, 0529488778, 0529565027</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2499,10 +2499,14 @@
       <c r="O23" t="b">
         <v>1</v>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/digital-launch.com</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Explore how to find Vietnam clothing manufacturers and the top 15 Vietnam Clothing Manufacturers 2026 such as Dugarco, Thygesen Textile,...</t>
+          <t>Digital Marketing Agency in Vietnam. Based in Ho Chi Minh City (Saigon) we provide the best digital marketing service to create brand awareness and followers</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
@@ -2512,13 +2516,13 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -2526,11 +2530,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB23" t="b">
-        <v>0</v>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2545,12 +2549,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://congcaphe.com/</t>
+          <t>https://dugarco.com/en/vietnam-clothing-manufacturers/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>cmo@congcaphe.com</t>
+          <t>dugarco@mayducgiang.com.vn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2560,12 +2564,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>cmo@congcaphe.com, fr.intl@congcaphe.com, fr@congcaphe.com</t>
+          <t>dugarco@mayducgiang.com.vn, info@dugarco.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0911811123</t>
+          <t>0902156565</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2588,8 +2592,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Mùa hè này, Cộng có mãng cầu.
-Còn bạn, chọn phiên bản “Ngầu” nào cho mình?</t>
+          <t>Explore how to find Vietnam clothing manufacturers and the top 15 Vietnam Clothing Manufacturers 2026 such as Dugarco, Thygesen Textile,...</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -2613,10 +2616,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="b">
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2632,12 +2635,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://dagiac.com/</t>
+          <t>https://congcaphe.com/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>dklong@dagiac.com</t>
+          <t>cmo@congcaphe.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2647,12 +2650,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>dklong@dagiac.com</t>
+          <t>cmo@congcaphe.com, fr.intl@congcaphe.com, fr@congcaphe.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0949998844, 0570189432</t>
+          <t>0911811123</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2672,14 +2675,11 @@
       <c r="O25" t="b">
         <v>1</v>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/dagiac</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>We are Full Service Digital Agency based in Ho Chi Minh helping foreign invested companies in Vietnam succeed with their Digital Marketing.</t>
+          <t>Mùa hè này, Cộng có mãng cầu.
+Còn bạn, chọn phiên bản “Ngầu” nào cho mình?</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="b">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2717,17 +2717,17 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://iscale-solutions.com/outsource-to-vietnam/</t>
+          <t>https://dagiac.com/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>info@iscale-solutions.com</t>
+          <t>dklong@dagiac.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>info@iscale-solutions.com</t>
+          <t>dklong@dagiac.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0312111054, 0971381476, 0525939362</t>
+          <t>0949998844, 0570189432</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/iscale-solutions</t>
+          <t>https://linkedin.com/company/dagiac</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Outsource to Vietnam for high-quality, cost-efficient business services. Tap into skilled expertise and innovative solutions to boost your success. Book today!</t>
+          <t>We are Full Service Digital Agency based in Ho Chi Minh helping foreign invested companies in Vietnam succeed with their Digital Marketing.</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -2793,11 +2793,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB26" t="b">
-        <v>1</v>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2812,7 +2812,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://iscale-solutions.com/outsource-to-vietnam/ai-machine-learning-specialists/</t>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0745102627, 0971381476, 0745101799</t>
+          <t>0312111054, 0971381476, 0525939362</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Outsource AI &amp; machine learning, algorithms with a top company in Vietnam. Expert in artificial intelligence and software outsourcing solutions.</t>
+          <t>Outsource to Vietnam for high-quality, cost-efficient business services. Tap into skilled expertise and innovative solutions to boost your success. Book today!</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
@@ -2883,10 +2883,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="b">
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2902,27 +2902,27 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.xtmobile.vn/</t>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/ai-machine-learning-specialists/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>tinhlexuan@gmail.com</t>
+          <t>info@iscale-solutions.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>❌ Bad</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tinhlexuan@gmail.com, xtmobile.sg@gmail.com, xtmobile_sg@yahoo.com</t>
+          <t>info@iscale-solutions.com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0754716982, 0515113368, 0909410102</t>
+          <t>0745102627, 0971381476, 0745101799</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2942,10 +2942,14 @@
       <c r="O28" t="b">
         <v>1</v>
       </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/iscale-solutions</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Hệ thống bán lẻ điện thoại Samsung, iPhone mới - cũ, iPad, MacBook, phụ kiện chính hãng, thu cũ đổi mới. XTmobile có 7 cửa hàng tại TPHCM.</t>
+          <t>Outsource AI &amp; machine learning, algorithms with a top company in Vietnam. Expert in artificial intelligence and software outsourcing solutions.</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
@@ -2955,7 +2959,7 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, IT Software, Multi-Email, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2969,11 +2973,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="b">
-        <v>0</v>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2983,20 +2987,32 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://wearefram.com/services/mobile-app-development/</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>https://www.xtmobile.vn/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>tinhlexuan@gmail.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>❌ Bad</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tinhlexuan@gmail.com, xtmobile.sg@gmail.com, xtmobile_sg@yahoo.com</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0821393511</t>
+          <t>0754716982, 0515113368, 0909410102</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3016,14 +3032,10 @@
       <c r="O29" t="b">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/fram</t>
-        </is>
-      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Custom mobile app development services company in Vietnam. fram^ has dedicated teams with the best developers to build you custom solutions.</t>
+          <t>Hệ thống bán lẻ điện thoại Samsung, iPhone mới - cũ, iPad, MacBook, phụ kiện chính hãng, thu cũ đổi mới. XTmobile có 7 cửa hàng tại TPHCM.</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
@@ -3033,7 +3045,7 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -3047,11 +3059,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="b">
-        <v>1</v>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3061,20 +3073,32 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nimblehq.co/locations/ho-chi-minh/</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/blockchain-developers/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0948190247, 0347230347, 0887549738</t>
+          <t>0745102627, 0971381476, 0745101799</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3096,12 +3120,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/nimblehq</t>
+          <t>https://linkedin.com/company/iscale-solutions</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Nimble is a web software &amp; mobile application development company in Ho Chi Minh City, Vietnam. We build innovative &amp; top notch digital solutions.</t>
+          <t>iScale Solutions is a top blockchain outsourcing and software development company in Vietnam, trusted by startups for expert smart contract and development services.</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
@@ -3117,7 +3141,7 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3125,11 +3149,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="b">
-        <v>0</v>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3144,7 +3168,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://wearefram.com/services/saas-development/</t>
+          <t>https://wearefram.com/services/mobile-app-development/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -3179,7 +3203,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Through an integrated and process-driven approach, fram^ offers SaaS development services needed for your product from start to finish.</t>
+          <t>Custom mobile app development services company in Vietnam. fram^ has dedicated teams with the best developers to build you custom solutions.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
@@ -3203,10 +3227,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB31" t="b">
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3222,7 +3246,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://innotech-vn.com/hire-mobile-app-developers-ios-android-in-vietnam/</t>
+          <t>https://nimblehq.co/locations/ho-chi-minh/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -3230,7 +3254,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0907896363</t>
+          <t>0948190247, 0347230347, 0887549738</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3252,12 +3276,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/30204055</t>
+          <t>https://linkedin.com/company/nimblehq</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Innotech Vietnam is reliable to hire mobile app developers (iOS/ Android) in Vietnam with the technically competent and creative bunch, attractive cost.</t>
+          <t>Nimble is a web software &amp; mobile application development company in Ho Chi Minh City, Vietnam. We build innovative &amp; top notch digital solutions.</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
@@ -3281,11 +3305,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="b">
-        <v>1</v>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3300,7 +3324,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.aegona.com/our-services/software-maintenance</t>
+          <t>https://wearefram.com/services/saas-development/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -3308,7 +3332,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0704550073, 0914518869</t>
+          <t>0821393511</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3330,12 +3354,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/aegona</t>
+          <t>https://linkedin.com/company/fram</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Ensure the smooth operation of your software with expert software maintenance services and keep your software up-to-date, secure, and optimized for peak performance.</t>
+          <t>Through an integrated and process-driven approach, fram^ offers SaaS development services needed for your product from start to finish.</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
@@ -3359,10 +3383,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB33" t="b">
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3378,27 +3402,15 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://ondigitals.com/</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>contact@ondigitals.com</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>🔵 Generic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>contact@ondigitals.com</t>
-        </is>
-      </c>
+          <t>https://innotech-vn.com/hire-mobile-app-developers-ios-android-in-vietnam/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0923150767, 0906648177, 0500363154</t>
+          <t>0907896363</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3416,16 +3428,16 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/on-digitals</t>
+          <t>https://linkedin.com/company/30204055</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Digital marketing services in HCMC, Vietnam from the top outsource marketing agency company, provide professional digital marketing solutions.</t>
+          <t>Innotech Vietnam is reliable to hire mobile app developers (iOS/ Android) in Vietnam with the technically competent and creative bunch, attractive cost.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
@@ -3435,7 +3447,7 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3449,10 +3461,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="b">
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3468,7 +3480,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://innotech-vn.com/top-ai-software-outsourcing-company-in-vietnam/</t>
+          <t>https://www.aegona.com/our-services/software-maintenance</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3476,7 +3488,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0907896363</t>
+          <t>0704550073, 0914518869</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3498,12 +3510,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/30204055</t>
+          <t>https://linkedin.com/company/aegona</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Building an internal AI engineering team is not only expensive but also time-consuming. This is why AI software outsourcing is becoming an increasingly...</t>
+          <t>Ensure the smooth operation of your software with expert software maintenance services and keep your software up-to-date, secure, and optimized for peak performance.</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
@@ -3527,10 +3539,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="b">
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3546,15 +3558,27 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.startus-insights.com/innovators-guide/global-startup-ecosystem/</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>https://ondigitals.com/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>contact@ondigitals.com</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>contact@ondigitals.com</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0588235294</t>
+          <t>0923150767, 0906648177, 0500363154</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3572,16 +3596,16 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/startus</t>
+          <t>https://linkedin.com/company/on-digitals</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Explore the 2026 startup ecosystem with insights on global rankings, capital flows, AI investments, and policies shaping innovation hubs worldwide.</t>
+          <t>Digital marketing services in HCMC, Vietnam from the top outsource marketing agency company, provide professional digital marketing solutions.</t>
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
@@ -3591,7 +3615,7 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, LinkedIn</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3605,46 +3629,34 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="b">
-        <v>0</v>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://remotepeople.com/glossary/outsourcing/</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>info@remotepeople.com</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>⚪ Low</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>info@remotepeople.com</t>
-        </is>
-      </c>
+          <t>https://innotech-vn.com/top-ai-software-outsourcing-company-in-vietnam/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0842767846</t>
+          <t>0907896363</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3658,26 +3670,20 @@
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="b">
-        <v>0</v>
-      </c>
-      <c r="M37" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/remotepeoplecom</t>
+          <t>https://linkedin.com/company/30204055</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
+          <t>Building an internal AI engineering team is not only expensive but also time-consuming. This is why AI software outsourcing is becoming an increasingly...</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -3687,32 +3693,40 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://horusent.com/</t>
+          <t>https://www.startus-insights.com/innovators-guide/global-startup-ecosystem/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -3720,7 +3734,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0720231536, 0862595405, 0720232048</t>
+          <t>0588235294</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3740,10 +3754,14 @@
       <c r="O38" t="b">
         <v>1</v>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/startus</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>We are a mobile game company in Vietnam with more than 7 years of experience working in the international gaming industry.</t>
+          <t>Explore the 2026 startup ecosystem with insights on global rankings, capital flows, AI investments, and policies shaping innovation hubs worldwide.</t>
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
@@ -3753,7 +3771,7 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3767,26 +3785,26 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="b">
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://crosstechcom.com/vietnam-web-development-company-revolutionizing-online-presence/</t>
+          <t>https://innotech-vn.com/bang-cach-nao-chatbot-mang-lai-loi-ich-cho-nhung-cong-ty-fintech/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3794,7 +3812,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0741024107</t>
+          <t>0907896363</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3814,10 +3832,14 @@
       <c r="O39" t="b">
         <v>1</v>
       </c>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/30204055</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Learn how Vietnam's web development companies are revolutionizing online presence with quality, excellence, and cost-effective solutions. Look into offerings like digital marketing, mobile app development, e-commerce, and web design. Find the best web development company in Vietnam for your project</t>
+          <t>Sử dụng chatbot và trí tuệ nhân tạo cho phép các công ty fintech có thể cung cấp giá trị trải nghiệm gia tăng khác biệt đối với khách hàng của họ.</t>
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
@@ -3827,13 +3849,13 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -3841,26 +3863,26 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="b">
-        <v>0</v>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.icloud.com/</t>
+          <t>https://wearefram.com/services/ecommerce-development/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3868,12 +3890,12 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0505161291</t>
+          <t>0821393511</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mobile Dev</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3888,10 +3910,14 @@
       <c r="O40" t="b">
         <v>1</v>
       </c>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/fram</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Log in to iCloud to access your photos, mail, notes, documents and more. Sign in with your AppleÂ Account or create a new account to start using Apple services.</t>
+          <t>Take a competitive, always-on approach to custom eCommerce development. Continually improve UI, UX and back-end infrastructure for a market-leading customer experience.</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
@@ -3901,13 +3927,13 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Has Phone, Mobile Dev, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -3915,11 +3941,11 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="b">
-        <v>0</v>
+      <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3929,20 +3955,32 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.viivue.com/project-type/web-development/</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>https://remotepeople.com/glossary/outsourcing/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>info@remotepeople.com</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>info@remotepeople.com</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0909690517</t>
+          <t>0842767846</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3956,20 +3994,26 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" t="b">
         <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/viivue-web-design-company</t>
+          <t>https://linkedin.com/company/remotepeoplecom</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Our process and thirst for knowledge enable us to design, redesign and build websites for clients across a wide range of industries — from education, hospitality, and healthcare to B2B services, manufacturing, and emerging technologies. We take time to understand each client’s business model, user n</t>
+          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
@@ -3985,20 +4029,12 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>enterprise</t>
-        </is>
-      </c>
-      <c r="AA41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="b">
-        <v>0</v>
-      </c>
+          <t>20260515_143249</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4007,37 +4043,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://phuoc-associates.com/practice/investment-in-viet-nam/</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>info@phuoc-partner.com</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>⚪ Low</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>info@phuoc-partner.com</t>
-        </is>
-      </c>
+          <t>https://horusent.com/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0822252301</t>
+          <t>0720231536, 0862595405, 0720232048</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4052,14 +4076,10 @@
       <c r="O42" t="b">
         <v>1</v>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/phuoc-associates-law-firm</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Phuoc &amp; Associates one of the largest law firms in Vietnam, is a veteran specialist in providing legal services to foreign investors entering the Vietnamese market</t>
+          <t>We are a mobile game company in Vietnam with more than 7 years of experience working in the international gaming industry.</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -4069,7 +4089,7 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Has Phone, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4083,10 +4103,10 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="b">
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4097,12 +4117,12 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
+          <t>https://crosstechcom.com/vietnam-web-development-company-revolutionizing-online-presence/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -4110,12 +4130,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0760182730, 0554503546, 0392421401</t>
+          <t>0741024107</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mobile Dev</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4124,22 +4144,16 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M43" t="b">
-        <v>0</v>
-      </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Từ điển Hán Nôm - Tra từ: công</t>
+          <t>Learn how Vietnam's web development companies are revolutionizing online presence with quality, excellence, and cost-effective solutions. Look into offerings like digital marketing, mobile app development, e-commerce, and web design. Find the best web development company in Vietnam for your project</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -4149,18 +4163,26 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Has Phone, Mobile Dev</t>
+          <t>Has Phone, IT Software, Hiring</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4169,37 +4191,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://msmobile.vn/</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>msmobilevncom@gmail.com</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>❌ Bad</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>msmobilevncom@gmail.com, vandieutot@gmail.com</t>
-        </is>
-      </c>
+          <t>https://www.icloud.com/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0906655655, 0965112345, 0913087295</t>
+          <t>0505161291</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>Mobile Dev</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4212,12 +4222,12 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>MSmobile chuyên bán điện thoại xách tay chính hãng, điện thoại cũ 99% giá rẻ, Máy tính bảng, Tablet, Phụ kiện chính hãng uy tín hàng đầu Việt Nam,msmobile.vn</t>
+          <t>Log in to iCloud to access your photos, mail, notes, documents and more. Sign in with your AppleÂ Account or create a new account to start using Apple services.</t>
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
@@ -4227,7 +4237,7 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, Multi-Email</t>
+          <t>Has Phone, Mobile Dev, Hiring</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4241,10 +4251,410 @@
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB44" t="b">
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.thaiware.com/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0515163941, 0515175030, 0525092414</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>ศูนย์รวมโปรแกรมฟรี ไทย และเทศ อันดับ 1 รวมข่าวสาระน่ารู้ด้านไอที ทิปส์เทคนิคใช้งาน รีวิวสินค้า เช็ครอบหนัง หนังมาใหม่ รีวิวหนัง พร้อมเครื่องมือออนไลน์</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>20260515_203003</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>12</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.viivue.com/project-type/web-development/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0909690517</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/viivue-web-design-company</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Our process and thirst for knowledge enable us to design, redesign and build websites for clients across a wide range of industries — from education, hospitality, and healthcare to B2B services, manufacturing, and emerging technologies. We take time to understand each client’s business model, user n</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>11</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://phuoc-associates.com/practice/investment-in-viet-nam/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>info@phuoc-partner.com</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>info@phuoc-partner.com</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0822252301</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Web Design</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/phuoc-associates-law-firm</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Phuoc &amp; Associates one of the largest law firms in Vietnam, is a veteran specialist in providing legal services to foreign investors entering the Vietnamese market</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Has Phone, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0760182730, 0554503546, 0392421401</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Từ điển Hán Nôm - Tra từ: công</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>20260515_143249</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://msmobile.vn/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>msmobilevncom@gmail.com</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>❌ Bad</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>msmobilevncom@gmail.com, vandieutot@gmail.com</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0906655655, 0965112345, 0913087295</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Web Design</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>MSmobile chuyên bán điện thoại xách tay chính hãng, điện thoại cũ 99% giá rẻ, Máy tính bảng, Tablet, Phụ kiện chính hãng uy tín hàng đầu Việt Nam,msmobile.vn</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, Multi-Email</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
         <v>0</v>
       </c>
     </row>

--- a/leads_ALL.xlsx
+++ b/leads_ALL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0749259041, 0909686810, 0311850627</t>
+          <t>0526105018, 0909686810, 0384104664</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -634,17 +634,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -663,18 +657,26 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Sales/HR Email, Has Phone, VN Domain, IT Software, Multi-Email, LinkedIn</t>
+          <t>Sales/HR Email, Has Phone, VN Domain, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+          <t>20260518_230552</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1033,17 +1035,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.orientsoftware.com/</t>
+          <t>https://www.edvido.com/digital-marketing-agencies/ho-chi-minh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sales@orientsoftware.com</t>
+          <t>business@align.vn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1053,12 +1055,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sales@orientsoftware.com, career@orientsoftware.com, contact@orientsoftware.com</t>
+          <t>business@align.vn, contact@lesmichels.fr, digital@x-dmaic.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0963736699, 0938390299</t>
+          <t>0800000429, 0985242099, 0723352062</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,10 +1080,14 @@
       <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/edvido</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Trusted by 200+ global clients, Orient Software Development Corporation is a leading software development company in Vietnam delivering innovative solutions through flexible outsourcing service models.</t>
+          <t>Edvido allows you to connect with the best digital marketing agencies in Hồ Chí Minh by helping you to compare different agencies' portfolios and reviews.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1091,13 +1097,13 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Sales/HR Email, Has Phone, IT Software, Multi-Email, Hiring</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260518_230552</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1124,12 +1130,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://reliasoftware.com/industries/ecommerce-app-development</t>
+          <t>https://www.orientsoftware.com/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sales@reliasoftware.com</t>
+          <t>sales@orientsoftware.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1139,12 +1145,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>sales@reliasoftware.com</t>
+          <t>sales@orientsoftware.com, career@orientsoftware.com, contact@orientsoftware.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0972016100</t>
+          <t>0963736699, 0938390299</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,14 +1170,10 @@
       <c r="O8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/relia-software</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Looking for an E-commerce Mobile App Development Company? We Provide the best E-commerce mobile app development services for your business. Talk to us now!</t>
+          <t>Trusted by 200+ global clients, Orient Software Development Corporation is a leading software development company in Vietnam delivering innovative solutions through flexible outsourcing service models.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1181,7 +1183,7 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Sales/HR Email, Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1214,27 +1216,27 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.talentnetgroup.com/locations/ho-chi-minh-office</t>
+          <t>https://reliasoftware.com/industries/ecommerce-app-development</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>talentnet.cambodia@talentnetgroup.com</t>
+          <t>sales@reliasoftware.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>✅ Sales/HR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>talentnet.cambodia@talentnetgroup.com, contact-hcm@talentnetgroup.com, mike.hebert@talentnetgroup.com</t>
+          <t>sales@reliasoftware.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0949105144, 0854126856, 0305202145</t>
+          <t>0972016100</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1256,12 +1258,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/talentnet-corporation</t>
+          <t>https://linkedin.com/company/relia-software</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6th Floor, Star Building, 33 Mac Dinh Chi, District 1, Ho Chi Minh City, Vietnam</t>
+          <t>Looking for an E-commerce Mobile App Development Company? We Provide the best E-commerce mobile app development services for your business. Talk to us now!</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1271,7 +1273,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+          <t>Sales/HR Email, Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1286,7 +1288,7 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
@@ -1299,32 +1301,32 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://softvn.vn/</t>
+          <t>https://www.talentnetgroup.com/locations/ho-chi-minh-office</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>email@domain.com</t>
+          <t>talentnet.cambodia@talentnetgroup.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>email@domain.com</t>
+          <t>talentnet.cambodia@talentnetgroup.com, contact-hcm@talentnetgroup.com, mike.hebert@talentnetgroup.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0868128213, 0868218213, 0578492573</t>
+          <t>0949105144, 0854126856, 0305202145</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,10 +1346,14 @@
       <c r="O10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/talentnet-corporation</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Mua, bán phần mềm bản quyền, software bản quyền chính hãng giá rẻ, giao hàng toàn quốc, dịch vụ triển khai chuyên nghiệp và nhanh chóng tại SOFTVN.</t>
+          <t>6th Floor, Star Building, 33 Mac Dinh Chi, District 1, Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1357,7 +1363,7 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, IT Software, Hiring</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1375,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1385,32 +1391,32 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://tuyensinh.uel.edu.vn/nganh-cong-nghe-tai-chinh-la-gi/</t>
+          <t>https://replus.vn/cong-ty-startup-thanh-cong-tai-viet-nam/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>phonghanhchinh@uel.edu.vn</t>
+          <t>info@replus.com.vn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>phonghanhchinh@uel.edu.vn, cntt@uel.edu.vn, tuvantuyensinh@uel.edu.vn</t>
+          <t>info@replus.com.vn, info@replus.vn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0888247669, 0708247669</t>
+          <t>0903009656, 0932678626, 0932789656</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1428,12 +1434,12 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Được xem là một làn sóng mới ưu việt, công nghệ tài chính Fintech đã làm thay đổi toàn bộ cách thức cung ứng, vận hành các dịch vụ tài chính. Cũng như mô hình tổ chức đã có từ trước đến nay. Vậy ngành công nghệ tài chính sẽ học những gì? Ở đâu đào tạo đảm bảo chất lượng và uy tín? Triển vọng nghề ng</t>
+          <t>Những năm qua, trào lưu Startup trở nên sôi động hơn bao giờ hết. Cùng khám phá thông tin về các công ty startup thành công tại Việt Nam</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1443,13 +1449,13 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, IT Software, Multi-Email</t>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260518_230552</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1471,17 +1477,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://genk.vn/</t>
+          <t>https://softvn.vn/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>giaitrixahoi@admicro.vn</t>
+          <t>email@domain.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1491,12 +1497,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>giaitrixahoi@admicro.vn, info@genk.vn</t>
+          <t>email@domain.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0965671778, 0522434621, 0596751139</t>
+          <t>0868128213, 0868218213, 0578492573</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1514,12 +1520,12 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>GenK là Website uy tín số 1 Việt Nam cung cấp cho bạn những thông tin mới nhất về công nghệ và thế giới Internet,tin tức sản phẩm cong nghe mới.</t>
+          <t>Mua, bán phần mềm bản quyền, software bản quyền chính hãng giá rẻ, giao hàng toàn quốc, dịch vụ triển khai chuyên nghiệp và nhanh chóng tại SOFTVN.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1529,7 +1535,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, IT Software, Multi-Email</t>
+          <t>Has Phone, VN Domain, IT Software, Hiring</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1544,7 +1550,7 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1557,17 +1563,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://hblabgroup.com/ai-outsourcing-company-in-vietnam/</t>
+          <t>https://tuyensinh.uel.edu.vn/nganh-cong-nghe-tai-chinh-la-gi/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>contact@hblab.vn</t>
+          <t>phonghanhchinh@uel.edu.vn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1577,12 +1583,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>contact@hblab.vn, cs_gl@hblab.vn</t>
+          <t>phonghanhchinh@uel.edu.vn, cntt@uel.edu.vn, tuvantuyensinh@uel.edu.vn</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0983098304, 0362819068</t>
+          <t>0888247669, 0708247669</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1600,16 +1606,12 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/hblab</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Choosing the right AI outsourcing company in Vietnam is a strategic decision shaped by talent depth, regulatory maturity, and the speed at which a partner can</t>
+          <t>Được xem là một làn sóng mới ưu việt, công nghệ tài chính Fintech đã làm thay đổi toàn bộ cách thức cung ứng, vận hành các dịch vụ tài chính. Cũng như mô hình tổ chức đã có từ trước đến nay. Vậy ngành công nghệ tài chính sẽ học những gì? Ở đâu đào tạo đảm bảo chất lượng và uy tín? Triển vọng nghề ng</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1619,7 +1621,7 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1637,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1652,27 +1654,27 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://civiloutsourcing.com/outsourcing-in-vietnam/</t>
+          <t>https://genk.vn/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>contact@civiloutsourcing.com</t>
+          <t>giaitrixahoi@admicro.vn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>contact@civiloutsourcing.com, aiden@civiloutsourcing.com</t>
+          <t>giaitrixahoi@admicro.vn, info@genk.vn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0935012378, 0906013469</t>
+          <t>0965671778, 0522434621, 0596751139</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1690,16 +1692,12 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/civil-engineering-outsourcing-services</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>As civil engineering and land survey firms face tighter deadlines, rising costs, and growing client demands, many are turning to global support to stay competitive. Among all outsourcing destinations, Vietnam outsourcing stands out as a strategic choice—especially for companies in the United States,</t>
+          <t>GenK là Website uy tín số 1 Việt Nam cung cấp cho bạn những thông tin mới nhất về công nghệ và thế giới Internet,tin tức sản phẩm cong nghe mới.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1709,7 +1707,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1727,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1742,32 +1740,32 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://mobileworld.com.vn/</t>
+          <t>https://hblabgroup.com/ai-outsourcing-company-in-vietnam/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>support@mobileworld.com.vn</t>
+          <t>contact@hblab.vn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>support@mobileworld.com.vn</t>
+          <t>contact@hblab.vn, cs_gl@hblab.vn</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0965287989, 0961273979</t>
+          <t>0983098304, 0362819068</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mobile Dev</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1782,10 +1780,14 @@
       <c r="O15" t="b">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/hblab</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Hệ thống bán lẻ điện thoại, máy tính bảng, Smart watch tại Tp.HCM ✓Uy tín ✓Giá rẻ nhất ✓Trả góp 0% ✓Chính hãng ✓Giao toàn quốc. 0965 28 79 89</t>
+          <t>Choosing the right AI outsourcing company in Vietnam is a strategic decision shaped by talent depth, regulatory maturity, and the speed at which a partner can</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1795,7 +1797,7 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, Mobile Dev, Hiring</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1813,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1823,32 +1825,32 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.jobthai.com/en/company/267137</t>
+          <t>https://civiloutsourcing.com/outsourcing-in-vietnam/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>sale@jobthai.com</t>
+          <t>contact@civiloutsourcing.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>sale@jobthai.com, support@jobthai.com</t>
+          <t>contact@civiloutsourcing.com, aiden@civiloutsourcing.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0929138383</t>
+          <t>0935012378, 0906013469</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1870,13 +1872,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/jobthai</t>
+          <t>https://linkedin.com/company/civil-engineering-outsourcing-services</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Jobs at QAi Consulting and Services QAi Consulting, we are business partnership to providing consultancy services in many areas to help your business moving faster with high quality services deliver to customers and help transforming your business to digitalize organization.
-Today technology disr</t>
+          <t>As civil engineering and land survey firms face tighter deadlines, rising costs, and growing client demands, many are turning to global support to stay competitive. Among all outsourcing destinations, Vietnam outsourcing stands out as a strategic choice—especially for companies in the United States,</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1897,14 +1898,14 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>enterprise</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1914,37 +1915,37 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://digital-launch.com/web-development-outsourcing-vietnam/</t>
+          <t>https://mobileworld.com.vn/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>hello@digital-launch.com</t>
+          <t>support@mobileworld.com.vn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>hello@digital-launch.com</t>
+          <t>support@mobileworld.com.vn</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0992229024, 0529488778, 0529565027</t>
+          <t>0965287989, 0961273979</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IT Software</t>
+          <t>Mobile Dev</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1959,14 +1960,10 @@
       <c r="O17" t="b">
         <v>1</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/digital-launch.com</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Web development outsourcing Vietnam | Outsource your WordPress, Magento or custom web development to our skilled team in Ho Chi Minh City (Saigon)</t>
+          <t>Hệ thống bán lẻ điện thoại, máy tính bảng, Smart watch tại Tp.HCM ✓Uy tín ✓Giá rẻ nhất ✓Trả góp 0% ✓Chính hãng ✓Giao toàn quốc. 0965 28 79 89</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -1976,7 +1973,7 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, VN Domain, Mobile Dev, Hiring</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1994,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2004,17 +2001,17 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://digital-launch.com/digital-agency-saigon/</t>
+          <t>https://www.edvido.com/pr-agencies/ho-chi-minh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>hello@digital-launch.com</t>
+          <t>hello@eloqasia.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2024,12 +2021,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>hello@digital-launch.com</t>
+          <t>hello@eloqasia.com, hello@phibious.com, baogia@dmvgroup.vn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0992229024, 0529488778, 0529565027</t>
+          <t>0800000429, 0985242099, 0723352062</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2051,12 +2048,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/digital-launch.com</t>
+          <t>https://linkedin.com/company/edvido</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Digital Agency in Saigon or Ho Chi Minh City that builds unique websites, does social media marketing and search engine optimization. Get ready to launch!</t>
+          <t>Edvido allows you to connect with the best pr agencies in Hồ Chí Minh by helping you to compare different agencies' portfolios and reviews.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2066,13 +2063,13 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260518_230552</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2094,17 +2091,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://vietanlaw.com/utility-services-in-business-establishment-procedures-in-hanoi/</t>
+          <t>https://www.jobthai.com/en/company/267137</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>info@vietanlaw.com</t>
+          <t>sale@jobthai.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2114,12 +2111,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>info@vietanlaw.com, info@vietanlaw.vn</t>
+          <t>sale@jobthai.com, support@jobthai.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0984291372, 0577055285, 0805188828</t>
+          <t>0929138383</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2141,12 +2138,13 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/viet-an-law</t>
+          <t>https://linkedin.com/company/jobthai</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Towards e-government suitable for the 4.0 technology era, the business registration procedure in Hanoi is considered a pioneering breakthrough in the</t>
+          <t>Jobs at QAi Consulting and Services QAi Consulting, we are business partnership to providing consultancy services in many areas to help your business moving faster with high quality services deliver to customers and help transforming your business to digitalize organization.
+Today technology disr</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2167,11 +2165,11 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>enterprise</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2189,27 +2187,27 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://vietanlaw.com/fintech-company-establishment-in-vietnam-under-sandbox-regulatory/</t>
+          <t>https://digital-launch.com/web-development-outsourcing-vietnam/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>info@vietanlaw.com</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>info@vietanlaw.com, info@vietanlaw.vn</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0984291372, 0577055285, 0805188828</t>
+          <t>0992229024, 0529488778, 0529565027</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2231,12 +2229,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/viet-an-law</t>
+          <t>https://linkedin.com/company/digital-launch.com</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>The rapid rise of financial technology (Fintech) has brought profound changes to the financial and banking services sector, with the emergence of various</t>
+          <t>Web development outsourcing Vietnam | Outsource your WordPress, Magento or custom web development to our skilled team in Ho Chi Minh City (Saigon)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2246,7 +2244,7 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2264,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2279,27 +2277,27 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.wdsaigon.com/e-commerce-website-development-vietnam/</t>
+          <t>https://vietanlaw.com/utility-services-in-business-establishment-procedures-in-hanoi/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>contact@wdsaigon.com</t>
+          <t>info@vietanlaw.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>contact@wdsaigon.com</t>
+          <t>info@vietanlaw.com, info@vietanlaw.vn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0316755511, 0977163421</t>
+          <t>0984291372, 0577055285, 0805188828</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2321,12 +2319,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/web-design-saigon</t>
+          <t>https://linkedin.com/company/viet-an-law</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Our e-commerce website development in Vietnam is designed to convert visitors to customers at your online store! Get a new Store Website Design.</t>
+          <t>Towards e-government suitable for the 4.0 technology era, the business registration procedure in Hanoi is considered a pioneering breakthrough in the</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -2336,7 +2334,7 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2354,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2369,27 +2367,27 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://savvycomsoftware.com/services/it-outsourcing-services/</t>
+          <t>https://vietanlaw.com/fintech-company-establishment-in-vietnam-under-sandbox-regulatory/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>contact@savvycomsoftware.com</t>
+          <t>info@vietanlaw.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>🔵 Generic</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>contact@savvycomsoftware.com</t>
+          <t>info@vietanlaw.com, info@vietanlaw.vn</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0352287866, 0703611494, 0903552656</t>
+          <t>0984291372, 0577055285, 0805188828</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2411,12 +2409,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/765474</t>
+          <t>https://linkedin.com/company/viet-an-law</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Outsourcing Software Vietnam services will allow businesses to access expertise, improve core functions, benefit from scalability and security.</t>
+          <t>The rapid rise of financial technology (Fintech) has brought profound changes to the financial and banking services sector, with the emergence of various</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -2426,7 +2424,7 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2444,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2459,12 +2457,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://digital-launch.com/digital-marketing-agency-in-vietnam/</t>
+          <t>https://www.wdsaigon.com/e-commerce-website-development-vietnam/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>hello@digital-launch.com</t>
+          <t>contact@wdsaigon.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2474,12 +2472,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>hello@digital-launch.com</t>
+          <t>contact@wdsaigon.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0992229024, 0529488778, 0529565027</t>
+          <t>0316755511, 0977163421</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2501,12 +2499,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/digital-launch.com</t>
+          <t>https://linkedin.com/company/web-design-saigon</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Digital Marketing Agency in Vietnam. Based in Ho Chi Minh City (Saigon) we provide the best digital marketing service to create brand awareness and followers</t>
+          <t>Our e-commerce website development in Vietnam is designed to convert visitors to customers at your online store! Get a new Store Website Design.</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
@@ -2522,7 +2520,7 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>20260515_203003</t>
+          <t>20260515_200855</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -2544,32 +2542,32 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://dugarco.com/en/vietnam-clothing-manufacturers/</t>
+          <t>https://savvycomsoftware.com/services/it-outsourcing-services/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>dugarco@mayducgiang.com.vn</t>
+          <t>contact@savvycomsoftware.com</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>dugarco@mayducgiang.com.vn, info@dugarco.com</t>
+          <t>contact@savvycomsoftware.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0902156565</t>
+          <t>0352287866, 0703611494, 0903552656</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2589,10 +2587,14 @@
       <c r="O24" t="b">
         <v>1</v>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/765474</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Explore how to find Vietnam clothing manufacturers and the top 15 Vietnam Clothing Manufacturers 2026 such as Dugarco, Thygesen Textile,...</t>
+          <t>Outsourcing Software Vietnam services will allow businesses to access expertise, improve core functions, benefit from scalability and security.</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -2602,7 +2604,7 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2620,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2630,32 +2632,32 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://congcaphe.com/</t>
+          <t>https://digital-launch.com/digital-agency-saigon/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>cmo@congcaphe.com</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>cmo@congcaphe.com, fr.intl@congcaphe.com, fr@congcaphe.com</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0911811123</t>
+          <t>0529565027, 0529488778, 0992229024</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2675,11 +2677,14 @@
       <c r="O25" t="b">
         <v>1</v>
       </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/digital-launch.com</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Mùa hè này, Cộng có mãng cầu.
-Còn bạn, chọn phiên bản “Ngầu” nào cho mình?</t>
+          <t>Digital Agency in Saigon or Ho Chi Minh City that builds unique websites, does social media marketing and search engine optimization. Get ready to launch!</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -2689,13 +2694,13 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260518_230552</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -2704,10 +2709,10 @@
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2717,32 +2722,32 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://dagiac.com/</t>
+          <t>https://digital-launch.com/digital-marketing-agency-in-vietnam/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>dklong@dagiac.com</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>⚪ Low</t>
+          <t>🔵 Generic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>dklong@dagiac.com</t>
+          <t>hello@digital-launch.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0949998844, 0570189432</t>
+          <t>0529565027, 0529488778, 0992229024</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2764,12 +2769,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/dagiac</t>
+          <t>https://linkedin.com/company/digital-launch.com</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>We are Full Service Digital Agency based in Ho Chi Minh helping foreign invested companies in Vietnam succeed with their Digital Marketing.</t>
+          <t>Digital Marketing Agency in Vietnam. Based in Ho Chi Minh City (Saigon) we provide the best digital marketing service to create brand awareness and followers</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -2785,7 +2790,7 @@
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260518_230552</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -2794,10 +2799,10 @@
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2807,17 +2812,17 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://iscale-solutions.com/outsource-to-vietnam/</t>
+          <t>https://dugarco.com/en/vietnam-clothing-manufacturers/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>info@iscale-solutions.com</t>
+          <t>dugarco@mayducgiang.com.vn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2827,12 +2832,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>info@iscale-solutions.com</t>
+          <t>dugarco@mayducgiang.com.vn, info@dugarco.com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0312111054, 0971381476, 0525939362</t>
+          <t>0902156565</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2852,14 +2857,10 @@
       <c r="O27" t="b">
         <v>1</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/iscale-solutions</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Outsource to Vietnam for high-quality, cost-efficient business services. Tap into skilled expertise and innovative solutions to boost your success. Book today!</t>
+          <t>Explore how to find Vietnam clothing manufacturers and the top 15 Vietnam Clothing Manufacturers 2026 such as Dugarco, Thygesen Textile,...</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
@@ -2869,7 +2870,7 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2887,7 +2888,7 @@
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2897,17 +2898,17 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://iscale-solutions.com/outsource-to-vietnam/ai-machine-learning-specialists/</t>
+          <t>https://congcaphe.com/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>info@iscale-solutions.com</t>
+          <t>cmo@congcaphe.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2917,12 +2918,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>info@iscale-solutions.com</t>
+          <t>cmo@congcaphe.com, fr.intl@congcaphe.com, fr@congcaphe.com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0745102627, 0971381476, 0745101799</t>
+          <t>0911811123</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2942,14 +2943,11 @@
       <c r="O28" t="b">
         <v>1</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/iscale-solutions</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Outsource AI &amp; machine learning, algorithms with a top company in Vietnam. Expert in artificial intelligence and software outsourcing solutions.</t>
+          <t>Mùa hè này, Cộng có mãng cầu.
+Còn bạn, chọn phiên bản “Ngầu” nào cho mình?</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
@@ -2959,7 +2957,7 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2974,10 +2972,10 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2987,32 +2985,32 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.xtmobile.vn/</t>
+          <t>https://dagiac.com/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>tinhlexuan@gmail.com</t>
+          <t>dklong@dagiac.com</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>❌ Bad</t>
+          <t>⚪ Low</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tinhlexuan@gmail.com, xtmobile.sg@gmail.com, xtmobile_sg@yahoo.com</t>
+          <t>dklong@dagiac.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0754716982, 0515113368, 0909410102</t>
+          <t>0949998844, 0570189432</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3032,10 +3030,14 @@
       <c r="O29" t="b">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/dagiac</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Hệ thống bán lẻ điện thoại Samsung, iPhone mới - cũ, iPad, MacBook, phụ kiện chính hãng, thu cũ đổi mới. XTmobile có 7 cửa hàng tại TPHCM.</t>
+          <t>We are Full Service Digital Agency based in Ho Chi Minh helping foreign invested companies in Vietnam succeed with their Digital Marketing.</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
@@ -3045,7 +3047,7 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, IT Software, Multi-Email, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -3078,7 +3080,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://iscale-solutions.com/outsource-to-vietnam/blockchain-developers/</t>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3098,7 +3100,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0745102627, 0971381476, 0745101799</t>
+          <t>0312111054, 0971381476, 0525939362</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3125,7 +3127,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>iScale Solutions is a top blockchain outsourcing and software development company in Vietnam, trusted by startups for expert smart contract and development services.</t>
+          <t>Outsource to Vietnam for high-quality, cost-efficient business services. Tap into skilled expertise and innovative solutions to boost your success. Book today!</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
@@ -3141,7 +3143,7 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>20260515_203003</t>
+          <t>20260515_200855</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3163,20 +3165,32 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://wearefram.com/services/mobile-app-development/</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/ai-machine-learning-specialists/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0821393511</t>
+          <t>0745102627, 0971381476, 0745101799</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3198,12 +3212,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/fram</t>
+          <t>https://linkedin.com/company/iscale-solutions</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Custom mobile app development services company in Vietnam. fram^ has dedicated teams with the best developers to build you custom solutions.</t>
+          <t>Outsource AI &amp; machine learning, algorithms with a top company in Vietnam. Expert in artificial intelligence and software outsourcing solutions.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
@@ -3241,20 +3255,32 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nimblehq.co/locations/ho-chi-minh/</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>https://www.xtmobile.vn/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>tinhlexuan@gmail.com</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>❌ Bad</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tinhlexuan@gmail.com, xtmobile.sg@gmail.com, xtmobile_sg@yahoo.com</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0948190247, 0347230347, 0887549738</t>
+          <t>0754716982, 0515113368, 0909410102</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3274,14 +3300,10 @@
       <c r="O32" t="b">
         <v>1</v>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/nimblehq</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Nimble is a web software &amp; mobile application development company in Ho Chi Minh City, Vietnam. We build innovative &amp; top notch digital solutions.</t>
+          <t>Hệ thống bán lẻ điện thoại Samsung, iPhone mới - cũ, iPad, MacBook, phụ kiện chính hãng, thu cũ đổi mới. XTmobile có 7 cửa hàng tại TPHCM.</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
@@ -3291,7 +3313,7 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, VN Domain, IT Software, Multi-Email, Hiring</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3306,7 +3328,7 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -3319,20 +3341,32 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://wearefram.com/services/saas-development/</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>https://iscale-solutions.com/outsource-to-vietnam/blockchain-developers/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>info@iscale-solutions.com</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0821393511</t>
+          <t>0745102627, 0971381476, 0745101799</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3354,12 +3388,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/fram</t>
+          <t>https://linkedin.com/company/iscale-solutions</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Through an integrated and process-driven approach, fram^ offers SaaS development services needed for your product from start to finish.</t>
+          <t>iScale Solutions is a top blockchain outsourcing and software development company in Vietnam, trusted by startups for expert smart contract and development services.</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
@@ -3375,7 +3409,7 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -3402,7 +3436,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://innotech-vn.com/hire-mobile-app-developers-ios-android-in-vietnam/</t>
+          <t>https://wearefram.com/services/mobile-app-development/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -3410,7 +3444,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0907896363</t>
+          <t>0821393511</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3432,12 +3466,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/30204055</t>
+          <t>https://linkedin.com/company/fram</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Innotech Vietnam is reliable to hire mobile app developers (iOS/ Android) in Vietnam with the technically competent and creative bunch, attractive cost.</t>
+          <t>Custom mobile app development services company in Vietnam. fram^ has dedicated teams with the best developers to build you custom solutions.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
@@ -3480,7 +3514,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.aegona.com/our-services/software-maintenance</t>
+          <t>https://nimblehq.co/locations/ho-chi-minh/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3488,7 +3522,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0704550073, 0914518869</t>
+          <t>0948190247, 0347230347, 0887549738</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3510,12 +3544,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/aegona</t>
+          <t>https://linkedin.com/company/nimblehq</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Ensure the smooth operation of your software with expert software maintenance services and keep your software up-to-date, secure, and optimized for peak performance.</t>
+          <t>Nimble is a web software &amp; mobile application development company in Ho Chi Minh City, Vietnam. We build innovative &amp; top notch digital solutions.</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
@@ -3543,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3558,27 +3592,15 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://ondigitals.com/</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>contact@ondigitals.com</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🔵 Generic</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>contact@ondigitals.com</t>
-        </is>
-      </c>
+          <t>https://wearefram.com/services/saas-development/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0923150767, 0906648177, 0500363154</t>
+          <t>0821393511</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3596,16 +3618,16 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/on-digitals</t>
+          <t>https://linkedin.com/company/fram</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Digital marketing services in HCMC, Vietnam from the top outsource marketing agency company, provide professional digital marketing solutions.</t>
+          <t>Through an integrated and process-driven approach, fram^ offers SaaS development services needed for your product from start to finish.</t>
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
@@ -3615,7 +3637,7 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3630,7 +3652,7 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
         <v>1</v>
@@ -3648,7 +3670,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://innotech-vn.com/top-ai-software-outsourcing-company-in-vietnam/</t>
+          <t>https://innotech-vn.com/hire-mobile-app-developers-ios-android-in-vietnam/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -3683,7 +3705,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Building an internal AI engineering team is not only expensive but also time-consuming. This is why AI software outsourcing is becoming an increasingly...</t>
+          <t>Innotech Vietnam is reliable to hire mobile app developers (iOS/ Android) in Vietnam with the technically competent and creative bunch, attractive cost.</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -3726,7 +3748,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.startus-insights.com/innovators-guide/global-startup-ecosystem/</t>
+          <t>https://www.aegona.com/our-services/software-maintenance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -3734,7 +3756,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0588235294</t>
+          <t>0704550073, 0914518869</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3756,12 +3778,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/startus</t>
+          <t>https://linkedin.com/company/aegona</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Explore the 2026 startup ecosystem with insights on global rankings, capital flows, AI investments, and policies shaping innovation hubs worldwide.</t>
+          <t>Ensure the smooth operation of your software with expert software maintenance services and keep your software up-to-date, secure, and optimized for peak performance.</t>
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
@@ -3789,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3804,15 +3826,27 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://innotech-vn.com/bang-cach-nao-chatbot-mang-lai-loi-ich-cho-nhung-cong-ty-fintech/</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>https://ondigitals.com/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>contact@ondigitals.com</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🔵 Generic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>contact@ondigitals.com</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0907896363</t>
+          <t>0923150767, 0906648177, 0500363154</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3830,16 +3864,16 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/30204055</t>
+          <t>https://linkedin.com/company/on-digitals</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Sử dụng chatbot và trí tuệ nhân tạo cho phép các công ty fintech có thể cung cấp giá trị trải nghiệm gia tăng khác biệt đối với khách hàng của họ.</t>
+          <t>Digital marketing services in HCMC, Vietnam from the top outsource marketing agency company, provide professional digital marketing solutions.</t>
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
@@ -3849,13 +3883,13 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, LinkedIn</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>20260515_203003</t>
+          <t>20260515_200855</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -3864,7 +3898,7 @@
         </is>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>1</v>
@@ -3882,7 +3916,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://wearefram.com/services/ecommerce-development/</t>
+          <t>https://innotech-vn.com/top-ai-software-outsourcing-company-in-vietnam/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3890,7 +3924,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0821393511</t>
+          <t>0907896363</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3912,12 +3946,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/fram</t>
+          <t>https://linkedin.com/company/30204055</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Take a competitive, always-on approach to custom eCommerce development. Continually improve UI, UX and back-end infrastructure for a market-leading customer experience.</t>
+          <t>Building an internal AI engineering team is not only expensive but also time-consuming. This is why AI software outsourcing is becoming an increasingly...</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
@@ -3933,7 +3967,7 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>20260515_203003</t>
+          <t>20260515_200855</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -3951,36 +3985,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://remotepeople.com/glossary/outsourcing/</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>info@remotepeople.com</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>⚪ Low</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>info@remotepeople.com</t>
-        </is>
-      </c>
+          <t>https://www.startus-insights.com/innovators-guide/global-startup-ecosystem/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0842767846</t>
+          <t>0588235294</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3994,26 +4016,20 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/remotepeoplecom</t>
+          <t>https://linkedin.com/company/startus</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
+          <t>Explore the 2026 startup ecosystem with insights on global rankings, capital flows, AI investments, and policies shaping innovation hubs worldwide.</t>
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
@@ -4023,32 +4039,40 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://horusent.com/</t>
+          <t>https://innotech-vn.com/bang-cach-nao-chatbot-mang-lai-loi-ich-cho-nhung-cong-ty-fintech/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -4056,7 +4080,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0720231536, 0862595405, 0720232048</t>
+          <t>0907896363</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4076,10 +4100,14 @@
       <c r="O42" t="b">
         <v>1</v>
       </c>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/30204055</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>We are a mobile game company in Vietnam with more than 7 years of experience working in the international gaming industry.</t>
+          <t>Sử dụng chatbot và trí tuệ nhân tạo cho phép các công ty fintech có thể cung cấp giá trị trải nghiệm gia tăng khác biệt đối với khách hàng của họ.</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -4089,13 +4117,13 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -4104,25 +4132,25 @@
         </is>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://crosstechcom.com/vietnam-web-development-company-revolutionizing-online-presence/</t>
+          <t>https://wearefram.com/services/ecommerce-development/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -4130,7 +4158,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0741024107</t>
+          <t>0821393511</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4150,10 +4178,14 @@
       <c r="O43" t="b">
         <v>1</v>
       </c>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/fram</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Learn how Vietnam's web development companies are revolutionizing online presence with quality, excellence, and cost-effective solutions. Look into offerings like digital marketing, mobile app development, e-commerce, and web design. Find the best web development company in Vietnam for your project</t>
+          <t>Take a competitive, always-on approach to custom eCommerce development. Continually improve UI, UX and back-end infrastructure for a market-leading customer experience.</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -4163,13 +4195,13 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring</t>
+          <t>Has Phone, IT Software, Hiring, LinkedIn</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260515_203003</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -4178,33 +4210,45 @@
         </is>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.icloud.com/</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>https://blacksnetwork.net/diendongnguyen</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sale@dongnguyenelectric.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>sale@dongnguyenelectric.com</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0505161291</t>
+          <t>0899160677, 0734141714, 0733196638</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4227,7 +4271,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Log in to iCloud to access your photos, mail, notes, documents and more. Sign in with your AppleÂ Account or create a new account to start using Apple services.</t>
+          <t>Công ty TNHH Đông Nguyễn đơn vị kinh doanh thiết bị điện công nghiệp tại TPHCM và Đà Lạt là nhà cung cấp uy tín cho nhiều nhà máy và tập đoàn ở Việt Nam.Số 18 Nguyễn Thái Sơn, P3, Quận Gò Vấp, TPHCMsale@dongnguyenelectric.com0933.195.977https://dongnguyenelectric.com/</t>
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
@@ -4243,7 +4287,7 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>20260515_200855</t>
+          <t>20260518_230552</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -4252,7 +4296,7 @@
         </is>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -4270,15 +4314,27 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.thaiware.com/</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>https://remotepeople.com/glossary/outsourcing/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>info@remotepeople.com</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>info@remotepeople.com</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0515163941, 0515175030, 0525092414</t>
+          <t>0842767846</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4292,16 +4348,26 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
       <c r="O45" t="b">
-        <v>1</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/remotepeoplecom</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>ศูนย์รวมโปรแกรมฟรี ไทย และเทศ อันดับ 1 รวมข่าวสาระน่ารู้ด้านไอที ทิปส์เทคนิคใช้งาน รีวิวสินค้า เช็ครอบหนัง หนังมาใหม่ รีวิวหนัง พร้อมเครื่องมือออนไลน์</t>
+          <t>Discover outsourcing: its definition, types, and benefits. Learn how third-party providers can boost efficiency and cut costs for businesses.</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
@@ -4311,26 +4377,18 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, Hiring</t>
+          <t>Has Phone, IT Software, LinkedIn</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>20260515_203003</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>enterprise</t>
-        </is>
-      </c>
-      <c r="AA45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
+          <t>20260515_143249</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4339,12 +4397,12 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.viivue.com/project-type/web-development/</t>
+          <t>https://horusent.com/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -4352,7 +4410,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0909690517</t>
+          <t>0720231536, 0862595405, 0720232048</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4370,16 +4428,12 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="b">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/viivue-web-design-company</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Our process and thirst for knowledge enable us to design, redesign and build websites for clients across a wide range of industries — from education, hospitality, and healthcare to B2B services, manufacturing, and emerging technologies. We take time to understand each client’s business model, user n</t>
+          <t>We are a mobile game company in Vietnam with more than 7 years of experience working in the international gaming industry.</t>
         </is>
       </c>
       <c r="R46" t="inlineStr"/>
@@ -4389,7 +4443,7 @@
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Has Phone, IT Software, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4417,37 +4471,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://phuoc-associates.com/practice/investment-in-viet-nam/</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>info@phuoc-partner.com</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>⚪ Low</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>info@phuoc-partner.com</t>
-        </is>
-      </c>
+          <t>https://crosstechcom.com/vietnam-web-development-company-revolutionizing-online-presence/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0822252301</t>
+          <t>0741024107</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4462,14 +4504,10 @@
       <c r="O47" t="b">
         <v>1</v>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/phuoc-associates-law-firm</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Phuoc &amp; Associates one of the largest law firms in Vietnam, is a veteran specialist in providing legal services to foreign investors entering the Vietnamese market</t>
+          <t>Learn how Vietnam's web development companies are revolutionizing online presence with quality, excellence, and cost-effective solutions. Look into offerings like digital marketing, mobile app development, e-commerce, and web design. Find the best web development company in Vietnam for your project</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -4479,7 +4517,7 @@
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Has Phone, Hiring, LinkedIn</t>
+          <t>Has Phone, IT Software, Hiring</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -4494,7 +4532,7 @@
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -4507,12 +4545,12 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
+          <t>https://www.icloud.com/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -4520,7 +4558,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0760182730, 0554503546, 0392421401</t>
+          <t>0505161291</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4534,22 +4572,16 @@
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Từ điển Hán Nôm - Tra từ: công</t>
+          <t>Log in to iCloud to access your photos, mail, notes, documents and more. Sign in with your AppleÂ Account or create a new account to start using Apple services.</t>
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
@@ -4559,18 +4591,26 @@
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Has Phone, Mobile Dev</t>
+          <t>Has Phone, Mobile Dev, Hiring</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>20260515_143249</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4579,37 +4619,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://msmobile.vn/</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>msmobilevncom@gmail.com</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>❌ Bad</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>msmobilevncom@gmail.com, vandieutot@gmail.com</t>
-        </is>
-      </c>
+          <t>https://www.thaiware.com/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0906655655, 0965112345, 0913087295</t>
+          <t>0515163941, 0515175030, 0525092414</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>IT Software</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4622,12 +4650,12 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>MSmobile chuyên bán điện thoại xách tay chính hãng, điện thoại cũ 99% giá rẻ, Máy tính bảng, Tablet, Phụ kiện chính hãng uy tín hàng đầu Việt Nam,msmobile.vn</t>
+          <t>ศูนย์รวมโปรแกรมฟรี ไทย และเทศ อันดับ 1 รวมข่าวสาระน่ารู้ด้านไอที ทิปส์เทคนิคใช้งาน รีวิวสินค้า เช็ครอบหนัง หนังมาใหม่ รีวิวหนัง พร้อมเครื่องมือออนไลน์</t>
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
@@ -4637,24 +4665,723 @@
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Has Phone, VN Domain, Multi-Email</t>
+          <t>Has Phone, IT Software, Hiring</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
+          <t>20260515_203003</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.xtaypro.com/en/app_download</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0314106254</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="b">
+        <v>1</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Rent your spare baggage allowance and earn your flight ticket back! Traveling light? Good, but don't be wasteful. Rent it for a good price and someone will appreciate it. Join our community now.</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev, Hiring</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>20260518_230552</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>13</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.pinterest.com/dktechnical_11/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0315916462, 0714984662, 0554235375</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="b">
+        <v>1</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Công ty thiết kế Website DK Technical | DK Technical
+"DK Technical là công ty thiết kế website và app mobile uy tín, chuyên nghiệp tại TPHCM. Chúng tôi cam kết mang đến cho khách hàng những sản phẩm chất lượng với mức giá cạnh tranh nhất.
+Website: https://dktechnical.vn/
+Địa chỉ: 5A Văn Cao, Phú Thạ</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev, Hiring</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>20260518_230552</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>13</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.craftyconfessions.com/2015/08/happiness-is-warm-glue-gun-and-hot-cup.html</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0718879063, 0941498184, 0570979395</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="b">
+        <v>1</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>I can't believe I forgot to share this amazing life event with all of you: We bought our first house! Yippie! Along with this crazy adult de...</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, Hiring</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>20260518_230552</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>13</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://blacksnetwork.net/sieuthidl?lang=portuguese</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0899160677, 0734141714, 0733196043</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="b">
+        <v>1</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Công ty cung cấp dịch vụ thi công lắp đặt giàn phơi thông minh Duy Lợi, lưới an toàn ban công chung cư, bạt che nắng mưa, mái hiên di động Duy Lợi, cửa lưới chống muỗi, cầu thang dây cáp giá rẻ tại TP HCM và Hà Nội</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev, Hiring</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>20260518_230552</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>12</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.viivue.com/project-type/web-development/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0909690517</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/viivue-web-design-company</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Our process and thirst for knowledge enable us to design, redesign and build websites for clients across a wide range of industries — from education, hospitality, and healthcare to B2B services, manufacturing, and emerging technologies. We take time to understand each client’s business model, user n</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>20260515_200855</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>enterprise</t>
         </is>
       </c>
-      <c r="AA49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="n">
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://phuoc-associates.com/practice/investment-in-viet-nam/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>info@phuoc-partner.com</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>⚪ Low</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>info@phuoc-partner.com</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0822252301</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Web Design</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="b">
+        <v>1</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/phuoc-associates-law-firm</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Phuoc &amp; Associates one of the largest law firms in Vietnam, is a veteran specialist in providing legal services to foreign investors entering the Vietnamese market</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Has Phone, Hiring, LinkedIn</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://hvdic.thivien.net/hv/c%c3%b4ng</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0760182730, 0554503546, 0392421401</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Từ điển Hán Nôm - Tra từ: công</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Has Phone, Mobile Dev</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>20260515_143249</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.legend-shipping.com/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0949935340, 0962519758, 0533919791</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IT Software</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>LEGEND SHIPPING is an international freight forwarding logistics company based in Vietnam. The company offers a comprehensive door-to-door logistics service to every destination in the world.</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Has Phone, IT Software</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>20260518_230552</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://msmobile.vn/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>msmobilevncom@gmail.com</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>❌ Bad</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>msmobilevncom@gmail.com, vandieutot@gmail.com</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0906655655, 0965112345, 0913087295</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Web Design</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>MSmobile chuyên bán điện thoại xách tay chính hãng, điện thoại cũ 99% giá rẻ, Máy tính bảng, Tablet, Phụ kiện chính hãng uy tín hàng đầu Việt Nam,msmobile.vn</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Has Phone, VN Domain, Multi-Email</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>20260515_200855</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" t="n">
         <v>0</v>
       </c>
     </row>
